--- a/data_extactor/batch_10_fa/batch_0029_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0029_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe PageMaker | نرم‌افزار سوابق مراجعین | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار ارائه اطلاعات | James Frazier Associates DataStart | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Word | Netscape Navigator | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار زمان‌بندی | Social Solutions ETO | Social Work Software ClientTouch | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | Adobe PageMaker | نرم‌افزار سوابق مراجعین | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار ارائه اطلاعات | James Frazier Associates DataStart | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Word | Netscape Navigator | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار زمان‌بندی | Social Solutions ETO | Social Work Software ClientTouch | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | نظارت | تفکر انتقادی | نوشتن | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | فلسفه و الهیات</t>
+          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی ایده‌ها | خلاقیت | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | دید نزدیک | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | سر و کار داشتن با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | تکرار تصمیم‌گیری | موقعیت‌های تعارض | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تمرین پیشرفته | مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌شناسان بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | پزشکان طب خانواده | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | کاردرمانگران | دستیاران کاردرمانی | کمک‌کاردرمانگران | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توان‌بخشی | دستیاران خدمات اجتماعی و انسانی | مشاوران سوء مصرف مواد و اختلالات رفتاری</t>
+          <t>پرستاران پیشرفته روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | پزشکان خانواده | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | قانون و دولت | آموزش و پرورش | مدیریت و اداره</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | تقسیم توجه | تجسم | حافظه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | نزدیکی فیزیکی | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مشاوران، سایر | مشاوران سوء مصرف مواد و اختلالات رفتاری | مشاوران سلامت روان | درمانگران ازدواج و خانواده | مشاوران توان‌بخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | دستیاران خدمات اجتماعی و انسانی | مددکاران سلامت جامعه | متخصصان آموزش بهداشت | متخصصان خدمات اجتماعی و جامعه، سایر | افسران مشروط و متخصصان درمان اصلاحی | مدیران خدمات اجتماعی و جامعه | روان‌شناسان بالینی و مشاوره | روان‌شناسان مدرسه | معلمان مددکاری اجتماعی، پس از متوسطه | مدیران خدمات پزشکی و بهداشتی | روحانیون</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مشاوران، سایر | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران سلامت روان | درمانگران ازدواج و خانواده | مشاوران توانبخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | دستیاران خدمات اجتماعی و انسانی | مددکاران سلامت جامعه | متخصصان آموزش بهداشت | متخصصان خدمات اجتماعی و جامعه، سایر | افسران مشروط و متخصصان درمان اصلاحی | مدیران خدمات اجتماعی و جامعه | روان‌شناسان بالینی و مشاوره | روان‌شناسان مدرسه | مدرسان مددکاری اجتماعی، آموزش عالی | مدیران خدمات پزشکی و بهداشتی | روحانیون</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | نرم‌افزار وبلاگ‌نویسی | مراکز کنترل و پیشگیری از بیماری‌ها CDC WONDER | مراکز کنترل و پیشگیری از بیماری‌ها Epi Info | Edpuzzle | Facebook | JamBoard | LogMeIn GoToWebinar | نرم‌افزار MEDITECH | Mentimeter | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Visio | Microsoft Word | Padlet | نرم‌افزار مرورگر وب | نرم‌افزار Wiki</t>
+          <t>Adobe Photoshop | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | نرم‌افزار وبلاگ‌نویسی | Centers for Disease Control and Prevention CDC WONDER | Centers for Disease Control and Prevention Epi Info | Edpuzzle | Facebook | JamBoard | LogMeIn GoToWebinar | نرم‌افزار MEDITECH | Mentimeter | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Visio | Microsoft Word | Padlet | نرم‌افزار مرورگر وب | نرم‌افزار Wiki</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نوشتن | صحبت کردن | راهبردهای یادگیری | یادگیری فعال | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | اداری | روان‌شناسی | ایمنی و امنیت عمومی | ریاضیات | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | ارتباطات و رسانه | پزشکی و دندان‌پزشکی | مدیریت و اداره | درمان و مشاوره | پرسنل و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | اداری | روان‌شناسی | ایمنی و امنیت عمومی | ریاضیات | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | ارتباطات و رسانه | پزشکی و دندان‌پزشکی | مدیریت و اداره | درمان و مشاوره | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شنیداری | درک نوشتاری | بیان نوشتاری | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | استدلال قیاسی | روانی ایده‌ها | خلاقیت | نظم‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | تماس با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | سر و کار داشتن با مشتریان خارجی یا عموم مردم | تکرار تصمیم‌گیری | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | سخنرانی عمومی | صرف زمان برای نشستن | نزدیکی فیزیکی | اهمیت تکرار وظایف مشابه | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | سخنرانی عمومی | صرف زمان برای نشستن | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران متخصص بالینی | مددکاران سلامت جامعه | متخصصان تغذیه و رژیم‌درمانی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان انفورماتیک سلامت | معلمان تخصص‌های بهداشتی، پس از متوسطه | مددکاران اجتماعی مراقبت‌های بهداشتی | هماهنگ‌کنندگان آموزشی | مدیران خدمات پزشکی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | مربیان و معلمان پرستاری، پس از متوسطه | نمایندگان بیمار | پزشکان طب پیشگیری | پرستاران ثبت‌نام‌شده | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | مددکاران سلامت جامعه | متخصصان رژیم غذایی و تغذیه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان انفورماتیک سلامت | استادان تخصص‌های بهداشتی، پس از متوسطه | مددکاران اجتماعی مراقبت‌های بهداشتی | هماهنگ‌کنندگان آموزشی | مدیران خدمات پزشکی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | مربیان و استادان پرستاری، پس از متوسطه | نمایندگان بیمار | پزشکان طب پیشگیری | پرستاران ثبت‌شده | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نوشتن | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | اداری | خدمات مشتری و شخصی | آموزش و پرورش | رایانه و الکترونیک</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | اداری | خدمات مشتری و شخصی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | حساسیت به مسئله | استدلال قیاسی | درک شنیداری | استدلال استقرایی | بیان نوشتاری | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات</t>
+          <t>بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>تماس با دیگران | مکالمات تلفنی | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | سر و کار داشتن با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | محیط داخلی، دارای کنترل محیطی | فشار زمانی | اهمیت دقیق یا صحیح بودن | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه | تکرار تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | سر و کار داشتن با افراد خشن یا دارای پرخاشگری فیزیکی | در وسیله نقلیه محصور یا کار با تجهیزات محصور | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | نزدیکی فیزیکی | پیامد خطا</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | اهمیت دقیق یا درست بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | نزدیکی فیزیکی | پیامد خطا</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و افسران رسیدگی‌کننده | مأموران دادگاه | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | افسران اصلاحی و زندانبانان | معلمان عدالت کیفری و اجرای قانون، پس از متوسطه | کارآگاهان و بازرسان جنایی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | سرپرستان رده اول افسران اصلاحی | سرپرستان رده اول پلیس و کارآگاهان | مددکاران اجتماعی مراقبت‌های بهداشتی | قضات، قضات دادگاه و داوران | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | افسران گشت پلیس و کلانتر | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوء مصرف مواد و اختلالات رفتاری</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | ضابطان دادگستری | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | افسران اصلاح و تربیت و زندانبانان | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | کارآگاهان و بازرسان جنایی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول پلیس و کارآگاهان | مددکاران اجتماعی مراقبت‌های بهداشتی | قضات، قضات دادگاه‌های بدوی و قضات صلح | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | ماموران گشت پلیس و کلانتر | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | اداری | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | اداری | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شنیداری | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی ایده‌ها | استدلال استقرایی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | خلاقیت</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی ایده‌ها | استدلال استقرایی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | سر و کار داشتن با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل محیطی | فشار زمانی | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌پرستاران خانگی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | دستیاران کاردرمانی | نمایندگان بیمار | کمک‌پرستاران شخصی | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | مشاوران توان‌بخشی | روان‌شناسان مدرسه | مدیران خدمات اجتماعی و جامعه | مشاوران سوء مصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌یاران سلامت در منزل | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کمک‌یاران کاردرمانی | نمایندگان بیمار | کمک‌یاران مراقبت شخصی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدرسه | مدیران خدمات اجتماعی و جامعه | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | نوشتن | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | درک نوشتاری | تشخیص گفتار | وضوح گفتار | بیان نوشتاری | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | تقسیم توجه | خلاقیت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | سر و کار داشتن با مشتریان خارجی یا عموم مردم | تکرار تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران متخصص بالینی | متخصصان تغذیه و رژیم‌درمانی | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | هماهنگ‌کنندگان تناسب اندام و سلامتی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌پرستاران خانگی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | نمایندگان بیمار | کمک‌پرستاران شخصی | پزشکان طب پیشگیری | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوء مصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | متخصصان رژیم غذایی و تغذیه | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | هماهنگ‌کنندگان تناسب اندام و سلامتی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌یاران سلامت در منزل | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | نمایندگان بیمار | کمک‌یاران مراقبت شخصی | پزشکان طب پیشگیری | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نظارت | نوشتن</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | قانون و دولت | مدیریت و اداره</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | دید دور | حافظه | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | نزدیکی فیزیکی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دستیاران خدمات اجتماعی و انسانی | مددکاران سلامت جامعه | متخصصان آموزش بهداشت | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مددکاران اجتماعی، سایر | مشاوران، سایر | مشاوران سوء مصرف مواد و اختلالات رفتاری | مشاوران سلامت روان | مشاوران توان‌بخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | افسران مشروط و متخصصان درمان اصلاحی | مدیران خدمات اجتماعی و جامعه | روحانیون | مدیران، فعالیت‌ها و آموزش‌های مذهبی | جمع‌آوری‌کنندگان کمک مالی | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | متخصصان آموزش و توسعه | درمانگران ازدواج و خانواده</t>
+          <t>دستیاران خدمات اجتماعی و انسانی | مددکاران سلامت جامعه | متخصصان آموزش بهداشت | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مددکاران اجتماعی، سایر | مشاوران، سایر | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران سلامت روان | مشاوران توانبخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | افسران مشروط و متخصصان درمان اصلاحی | مدیران خدمات اجتماعی و جامعه | روحانیون | مدیران، فعالیت‌ها و آموزش‌های مذهبی | جمع‌آوری‌کنندگان کمک مالی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | متخصصان آموزش و توسعه | درمانگران ازدواج و خانواده</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | درمان و مشاوره | ارتباطات و رسانه | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | پرسنل و منابع انسانی | اداری | ایمنی و امنیت عمومی | هنرهای زیبا</t>
+          <t>فلسفه و الهیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | درمان و مشاوره | ارتباطات و رسانه | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | پرسنل و منابع انسانی | اداری | ایمنی و امنیت عمومی | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شنیداری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک نوشتاری | بیان نوشتاری | روانی ایده‌ها | خلاقیت | نظم‌دهی اطلاعات | دید نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حافظه | دید دور | انعطاف‌پذیری بستار</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک کتبی | بیان کتبی | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حفظ کردن | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | تماس با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | فشار زمانی | تکرار تصمیم‌گیری | سخنرانی عمومی | نتایج کاری و نتایج سایر کارکنان | سر و کار داشتن با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا صحیح بودن</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | فشار زمانی | فراوانی تصمیم‌گیری | سخنرانی عمومی | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزش، مهدکودک تا متوسطه | مدیران آموزش، پس از متوسطه | معلمان آموزش، پس از متوسطه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مرده‌شویان، متصدیان کفن و دفن و برگزارکنندگان مراسم ترحیم | معلمان فلسفه و دین، پس از متوسطه | مشاوران توان‌بخشی | مشاوران مسکونی | معلمان مددکاری اجتماعی، پس از متوسطه | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مدیران مراسم تشییع، دفن و آرایشگران متوفی | اساتید فلسفه و دین، پس از متوسطه | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | مدرسان مددکاری اجتماعی، آموزش عالی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نوشتن | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | درک نوشتاری | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شنیداری | استدلال قیاسی | حساسیت به مسئله | خلاقیت | روانی ایده‌ها | استدلال استقرایی | نظم‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
+          <t>بیان کتبی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | اصالت | روانی ایده‌ها | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن</t>
+          <t>تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون | مددکاران سلامت جامعه | مدیران آموزش، مهدکودک تا متوسطه | مدیران آموزش، پس از متوسطه | معلمان آموزش، پس از متوسطه | مدیران آموزش و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | هماهنگ‌کنندگان آموزشی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کارگران تفریحی | مشاوران توان‌بخشی | مشاوران مسکونی | معلمان مددکاری اجتماعی، پس از متوسطه | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و توسعه</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون | مددکاران سلامت جامعه | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | هماهنگ‌کنندگان آموزشی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کارکنان تفریحات | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | مدرسان مددکاری اجتماعی، آموزش عالی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و توسعه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نظارت | نوشتن</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | درمان و مشاوره | مدیریت و اداره</t>
+          <t>فلسفه و الهیات | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | دید دور | حافظه | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با مشتریان خارجی یا عموم مردم | سخنرانی عمومی | نزدیکی فیزیکی | موقعیت‌های تعارض</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سخنرانی عمومی | نزدیکی فیزیکی | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>روحانیون | مدیران، فعالیت‌ها و آموزش‌های مذهبی | متخصصان خدمات اجتماعی و جامعه، سایر | دستیاران خدمات اجتماعی و انسانی | مددکاران سلامت جامعه | متخصصان آموزش بهداشت | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی، سایر | مشاوران، سایر | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران سوء مصرف مواد و اختلالات رفتاری | مشاوران توان‌بخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | افسران مشروط و متخصصان درمان اصلاحی | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مدیران خدمات اجتماعی و جامعه | معلمان فلسفه و دین، پس از متوسطه | معلمان خودسازی</t>
+          <t>روحانیون | مدیران، فعالیت‌ها و آموزش‌های مذهبی | متخصصان خدمات اجتماعی و جامعه، سایر | دستیاران خدمات اجتماعی و انسانی | مددکاران سلامت جامعه | متخصصان آموزش بهداشت | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی، سایر | مشاوران، سایر | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران توانبخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | افسران مشروط و متخصصان درمان اصلاحی | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مدیران خدمات اجتماعی و جامعه | اساتید فلسفه و دین، پس از متوسطه | معلمان خودسازی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0029_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0029_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | فلسفه و الهیات</t>
+          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در نتیجه‌گیری | دید نزدیک | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روان‌پزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان نوروسایکولوژی بالینی | پرستاران بالینی متخصص | روان‌شناسان بالینی و مشاوره | رابطان سلامت و بهورزان | پزشکان عمومی و خانواده | مددکاران اجتماعی بخش سلامت | درمانگران ازدواج و خانواده | مشاوران سلامت روان | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | کمک‌بهیاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران حوزه اوقات فراغت | مشاوران توان‌بخشی | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>پرستاران تخصصی روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | پزشکان عمومی و خانواده | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | حقوق و امور دولتی | آموزش و پرورش | مدیریت و امور اداری</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه | تجسم و تصویرسازی ذهنی | حافظه و یادآوری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | سایر مشاوران | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران سلامت روان | درمانگران ازدواج و خانواده | مشاوران توان‌بخشی | مشاوران و راهنمایان تحصیلی و شغلی | دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت | سایر متخصصان خدمات اجتماعی و عمومی | افسران مراقبت‌های تعلیقی و متخصصان اصلاح و تربیت | مدیران خدمات اجتماعی و عمومی | روان‌شناسان بالینی و مشاوره | روان‌شناسان مدرسه | مدرسان مددکاری اجتماعی در آموزش عالی | مدیران خدمات بهداشتی و درمانی | روحانیون و مبلغان مذهبی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | سایر مشاوران | مشاوران اعتیاد و اختلالات رفتاری | مشاوران سلامت روان | درمانگران ازدواج و خانواده | مشاوران توانبخشی | مشاوران تحصیلی، شغلی و هدایت استعدادها | دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت و ارتقای سلامت | سایر متخصصان خدمات اجتماعی و عمومی | مددکاران قضایی و متخصصان اصلاح و تربیت | مدیران خدمات اجتماعی و خدمات مردمی | روان‌شناسان بالینی و مشاوران سلامت روان | روان‌شناسان مدارس | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | مدیران خدمات درمانی و بهداشتی | روحانیون و مبلغان مذهبی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و پرورش | زبان انگلیسی | امور دفتری و اداری | روان‌شناسی | ایمنی و امنیت عمومی | ریاضیات | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | ارتباطات و رسانه | پزشکی و دندان‌پزشکی | مدیریت و امور اداری | درمان و مشاوره | امور پرسنلی و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | اداری | روان‌شناسی | ایمنی و امنیت عمومی | ریاضیات | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | ارتباطات و رسانه | پزشکی و دندان‌پزشکی | مدیریت و اداره | درمان و مشاوره | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | استدلال قیاسی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران بالینی متخصص | رابطان سلامت و بهورزان | کارشناسان تغذیه و رژیم‌درمانی | مشاوران و راهنمایان تحصیلی و شغلی | کارشناسان انفورماتیک سلامت | مدرسان رشته‌های تخصصی سلامت در آموزش عالی | مددکاران اجتماعی بخش سلامت | هماهنگ‌کنندگان برنامه‌های درسی و آموزشی | مدیران خدمات بهداشتی و درمانی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران دوره‌دیده مراقبت‌های پیشرفته | مربیان و مدرسان پرستاری در آموزش عالی | کارشناسان تکریم ارباب‌رجوع در مراکز درمانی | پزشکان طب پیشگیری | پرستاران دارای پروانه | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران متخصص بالینی | رابطان سلامت و بهورزان | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مشاوران تحصیلی، شغلی و هدایت استعدادها | متخصصان انفورماتیک سلامت | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مددکاران اجتماعی بخش سلامت و درمان | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران خدمات درمانی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران بالینی پیشرفته | مربیان و استادان پرستاری دانشگاه | کارشناسان امور بیماران و پذیرش | متخصصان پزشکی اجتماعی و طب پیشگیری | پرستاران | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حقوق و امور دولتی | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | امور دفتری و اداری | خدمات مشتریان و خدمات فردی | آموزش و پرورش | رایانه و الکترونیک</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | اداری | خدمات مشتری و شخصی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری و دادرسی | ضابطان و ماموران انتظامات دادگاه | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | زندانبانان و ماموران مراقبت زندان | مدرسان حقوق جزا و علوم انتظامی در آموزش عالی | کارآگاهان و بازرسان جنایی | مشاوران و راهنمایان تحصیلی و شغلی | سرپرستان رده‌اول زندانبانان | سرپرستان رده‌اول پلیس و کارآگاهان | مددکاران اجتماعی بخش سلامت | قضات و دادیاران دادگستری | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | ماموران گشت پلیس و کلانتری | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مأموران انتظامات و حفاظت دادگاه | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | مأموران زندان و بازداشتگاه | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | کارآگاهان و بازرسان جنایی | مشاوران تحصیلی، شغلی و هدایت استعدادها | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول پلیس و کارآگاهان | مددکاران اجتماعی بخش سلامت و درمان | قضات دادگاه و دادیاران | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | ماموران گشت پلیس و کلانتری | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | امور دفتری و اداری | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | اداری | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | استدلال استقرایی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری در نتیجه‌گیری | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | ابتکار و اصالت</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی ایده‌ها | استدلال استقرایی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | رابطان سلامت و بهورزان | مشاوران و راهنمایان تحصیلی و شغلی | کارشناسان آموزش بهداشت | مددکاران اجتماعی بخش سلامت | مراقبان سلامت در منزل | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | دستیاران کاردرمانی | کارشناسان تکریم ارباب‌رجوع در مراکز درمانی | مراقبان خدمات فردی | کمک‌بهیاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | درمانگران حوزه اوقات فراغت | مشاوران توان‌بخشی | روان‌شناسان مدرسه | مدیران خدمات اجتماعی و عمومی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | مراقبان سلامت و بهیاران مراقبت در منزل | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کمک‌یاران کاردرمانی | کارشناسان امور بیماران و پذیرش | مراقبان خدمات شخصی و همراهان توان‌خواهان | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | روان‌شناسان مدارس | مدیران خدمات اجتماعی و خدمات مردمی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و پرورش | مدیریت و امور اداری | پزشکی و دندان‌پزشکی | روان‌شناسی | امور دفتری و اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | مدیریت و اداره | پزشکی و دندان‌پزشکی | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | چابکی انگشتان | تقسیم توجه | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران بالینی متخصص | کارشناسان تغذیه و رژیم‌درمانی | مدیران فعالیت‌ها و آموزش‌های مذهبی | مشاوران و راهنمایان تحصیلی و شغلی | هماهنگ‌کنندگان تندرستی و سلامت جسمانی | کارشناسان آموزش بهداشت | مددکاران اجتماعی بخش سلامت | مراقبان سلامت در منزل | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کارشناسان تکریم ارباب‌رجوع در مراکز درمانی | مراقبان خدمات فردی | پزشکان طب پیشگیری | کمک‌بهیاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران متخصص بالینی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مدیران فعالیت‌ها و آموزش‌های مذهبی | مشاوران تحصیلی، شغلی و هدایت استعدادها | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | مراقبان سلامت و بهیاران مراقبت در منزل | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کارشناسان امور بیماران و پذیرش | مراقبان خدمات شخصی و همراهان توان‌خواهان | متخصصان پزشکی اجتماعی و طب پیشگیری | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | روان‌شناسی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | حقوق و امور دولتی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | حافظه و یادآوری | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | سایر مددکاران اجتماعی | سایر مشاوران | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران سلامت روان | مشاوران توان‌بخشی | مشاوران و راهنمایان تحصیلی و شغلی | افسران مراقبت‌های تعلیقی و متخصصان اصلاح و تربیت | مدیران خدمات اجتماعی و عمومی | روحانیون و مبلغان مذهبی | مدیران فعالیت‌ها و آموزش‌های مذهبی | کارشناسان جذب حمایت مالی و هدایا | برنامه‌ریزان گردهمایی‌ها، رویدادها و همایش‌ها | کارشناسان آموزش و توانمندسازی نیروی انسانی | درمانگران ازدواج و خانواده</t>
+          <t>دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مددکاران اجتماعی، سایر تخصص‌ها | سایر مشاوران | مشاوران اعتیاد و اختلالات رفتاری | مشاوران سلامت روان | مشاوران توانبخشی | مشاوران تحصیلی، شغلی و هدایت استعدادها | مددکاران قضایی و متخصصان اصلاح و تربیت | مدیران خدمات اجتماعی و خدمات مردمی | روحانیون و مبلغان مذهبی | مدیران فعالیت‌ها و آموزش‌های مذهبی | کارشناسان جذب منابع مالی و حامی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | کارشناسان آموزش و توسعه منابع انسانی | درمانگران ازدواج و خانواده</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و پرورش | درمان و مشاوره | ارتباطات و رسانه | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | امور پرسنلی و منابع انسانی | امور دفتری و اداری | ایمنی و امنیت عمومی | هنرهای تجسمی و نمایشی</t>
+          <t>فلسفه و الهیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | درمان و مشاوره | ارتباطات و رسانه | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | پرسنل و منابع انسانی | اداری | ایمنی و امنیت عمومی | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک کتبی | بیان کتبی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | مرتب‌سازی اطلاعات | دید نزدیک | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | حافظه و یادآوری | دید دور | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک کتبی | بیان کتبی | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حفظ کردن | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | رابطان سلامت و بهورزان | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی پیش‌دبستانی تا متوسطه | مدیران آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | مشاوران و راهنمایان تحصیلی و شغلی | کارشناسان آموزش بهداشت | مددکاران اجتماعی بخش سلامت | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مدیران امور آرامستان‌ها و تشریفات تدفین | مدرسان فلسفه و الهیات در آموزش عالی | مشاوران توان‌بخشی | مشاوران و سرپرستان خوابگاه‌ها | مدرسان مددکاری اجتماعی در آموزش عالی | مدیران خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مدیران و برگزارکنندگان مراسم تشییع و تدفین | مدرسان فلسفه و الهیات در آموزش عالی | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | آموزش و پرورش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | مدیریت و امور اداری | ایمنی و امنیت عمومی | امور پرسنلی و منابع انسانی | ارتباطات و رسانه</t>
+          <t>فلسفه و الهیات | آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | مدیریت و اداره | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی</t>
+          <t>بیان کتبی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | اصالت | روانی ایده‌ها | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون و مبلغان مذهبی | رابطان سلامت و بهورزان | مدیران آموزشی پیش‌دبستانی تا متوسطه | مدیران آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | مشاوران و راهنمایان تحصیلی و شغلی | کارشناسان آموزش بهداشت | مددکاران اجتماعی بخش سلامت | هماهنگ‌کنندگان برنامه‌های درسی و آموزشی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مربیان و کارشناسان فعالیت‌های اوقات فراغت | مشاوران توان‌بخشی | مشاوران و سرپرستان خوابگاه‌ها | مدرسان مددکاری اجتماعی در آموزش عالی | مدیران خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و توانمندسازی منابع انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون و مبلغان مذهبی | رابطان سلامت و بهورزان | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | زبان انگلیسی | خدمات مشتریان و خدمات فردی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | درمان و مشاوره | مدیریت و امور اداری</t>
+          <t>فلسفه و الهیات | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | حافظه و یادآوری | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>روحانیون و مبلغان مذهبی | مدیران فعالیت‌ها و آموزش‌های مذهبی | سایر متخصصان خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت | مددکاران اجتماعی کودک، خانواده و مدرسه | سایر مددکاران اجتماعی | سایر مشاوران | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران توان‌بخشی | مشاوران و راهنمایان تحصیلی و شغلی | افسران مراقبت‌های تعلیقی و متخصصان اصلاح و تربیت | مددکاران اجتماعی بخش سلامت | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مدیران خدمات اجتماعی و عمومی | مدرسان فلسفه و الهیات در آموزش عالی | مربیان و مدرسان دوره‌های آزاد و خودشکوفایی</t>
+          <t>روحانیون و مبلغان مذهبی | مدیران فعالیت‌ها و آموزش‌های مذهبی | سایر متخصصان خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی، سایر تخصص‌ها | سایر مشاوران | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران اعتیاد و اختلالات رفتاری | مشاوران توانبخشی | مشاوران تحصیلی، شغلی و هدایت استعدادها | مددکاران قضایی و متخصصان اصلاح و تربیت | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مدیران خدمات اجتماعی و خدمات مردمی | مدرسان فلسفه و الهیات در آموزش عالی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
